--- a/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_1.xlsx
+++ b/manuscript/submission_data/source_data/Source_Data_Supplementary_Figure_1.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_A" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_B" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel_C" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -455,7 +455,7 @@
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="25" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="21" customWidth="1" min="26" max="26"/>
     <col width="31" customWidth="1" min="27" max="27"/>
     <col width="36" customWidth="1" min="28" max="28"/>
     <col width="30" customWidth="1" min="29" max="29"/>
@@ -583,7 +583,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>manuscript/supplementary/Supplementary_Table_33_Sample_Frame_Reconciliation.tsv</t>
+          <t>manuscript/submission_data/audit_ledgers/supplementary_table_sources/Supplementary_Table_33_Sample_Frame_Reconciliation.tsv</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>passes_stage1_default_epoch_rule; mixed_or_partial_prn_epoch; passes_stage1_default_epoch_rule; informative_but_bounds_wide; prn_free_epoch</t>
+          <t>passes_stage1_default_epoch_rule; mixed_or_partial_prn_epoch; passes_stage1_default_epoch_rule; prn_free_epoch</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3001,7 +3001,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>jpn_pre2012_mixed_ap</t>
+          <t>jpn_pre2012_mixed_ap; jpn_ap_without_prn</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -3041,17 +3041,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.6219512195121951</t>
+          <t>0.8536585365853658</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.4615384615384615</t>
+          <t>0.2333333333333333</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>jpn_pre2012_mixed_ap=23; jpn_ap_without_prn=28</t>
+          <t>jpn_pre2012_mixed_ap=23; jpn_ap_without_prn=47</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>jpn_pre2012_mixed_ap=0.233; jpn_ap_without_prn=0.462</t>
+          <t>jpn_pre2012_mixed_ap=0.233; jpn_ap_without_prn=0.096</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -3541,22 +3541,22 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>908</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>0.9705573080967402</t>
+          <t>0.9547844374342797</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>usa_wp_only=21; usa_transition_mixed=6; usa_ap_prn_background=896</t>
+          <t>usa_wp_only=21; usa_transition_mixed=6; usa_ap_prn_background=881</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>usa_wp_only=0.087; usa_transition_mixed=0.333; usa_ap_prn_background=0.025</t>
+          <t>usa_wp_only=0.087; usa_transition_mixed=0.333; usa_ap_prn_background=0.041</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>promoted_from_screening; passes_stage1_default_epoch_rule; promoted_from_screening; passes_stage1_default_epoch_rule; informative_but_bounds_wide</t>
+          <t>promoted_from_screening; passes_stage1_default_epoch_rule</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3768,7 +3768,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>gbr_wp_only</t>
+          <t>gbr_wp_only; gbr_ap_prn_positive</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -3808,17 +3808,17 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>0.5517241379310345</t>
+          <t>0.5862068965517241</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4285714285714285</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -3955,12 +3955,12 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>gbr_wp_only=8; gbr_ap_prn_positive=8</t>
+          <t>gbr_wp_only=8; gbr_ap_prn_positive=9</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>gbr_wp_only=0.429; gbr_ap_prn_positive=0.467</t>
+          <t>gbr_wp_only=0.429; gbr_ap_prn_positive=0.400</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>711</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4310,17 +4310,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>140</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>0.8343125734430082</t>
+          <t>0.8354876615746181</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>0.1617473435655254</t>
+          <t>0.1605667060212514</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -4461,12 +4461,12 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>chn_wp_only=0; chn_transition_mixed=0; chn_ap_mixed=710</t>
+          <t>chn_wp_only=0; chn_transition_mixed=0; chn_ap_mixed=711</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>chn_wp_only=1.000; chn_transition_mixed=NA; chn_ap_mixed=0.162</t>
+          <t>chn_wp_only=1.000; chn_transition_mixed=NA; chn_ap_mixed=0.161</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -4790,27 +4790,27 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>0.1111111111111111</t>
+          <t>0.8888888888888888</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -4947,12 +4947,12 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>esp_wp_only=0; esp_transition_mixed=0; esp_ap_with_prn=1; esp_booster_modified_uncertain=0</t>
+          <t>esp_wp_only=0; esp_transition_mixed=0; esp_ap_with_prn=1; esp_booster_modified_uncertain=7</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>esp_wp_only=NA; esp_transition_mixed=NA; esp_ap_with_prn=0.000; esp_booster_modified_uncertain=1.000</t>
+          <t>esp_wp_only=NA; esp_transition_mixed=NA; esp_ap_with_prn=0.000; esp_booster_modified_uncertain=0.125</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -5027,7 +5027,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5037,17 +5037,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>fin_wp_only=0; fin_ap_without_prn=0; fin_ap_with_prn=4</t>
+          <t>fin_wp_only=3; fin_ap_without_prn=0; fin_ap_with_prn=4</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fin_wp_only=1.000; fin_ap_without_prn=1.000; fin_ap_with_prn=0.000</t>
+          <t>fin_wp_only=0.769; fin_ap_without_prn=1.000; fin_ap_with_prn=0.000</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -5276,7 +5276,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5286,17 +5286,17 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6363636363636364</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>0.3888888888888888</t>
+          <t>0.2222222222222222</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -5437,12 +5437,12 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>fra_wp_only=0; fra_ap_mixed=11</t>
+          <t>fra_wp_only=0; fra_ap_mixed=14</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fra_wp_only=1.000; fra_ap_mixed=0.389</t>
+          <t>fra_wp_only=1.000; fra_ap_mixed=0.222</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>711</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>698</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>136</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -7429,7 +7429,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>0.018309859154929577</t>
+          <t>0.01828410689170183</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -7444,12 +7444,12 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>0.1770956316410862</t>
+          <t>0.17591499409681227</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>0.1617473435655254</t>
+          <t>0.16056670602125148</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -8473,12 +8473,12 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -8511,7 +8511,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr">
         <is>
@@ -8520,12 +8524,12 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
@@ -8535,7 +8539,7 @@
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AG78" t="inlineStr">
@@ -8679,7 +8683,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -8689,12 +8693,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -8727,7 +8731,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr">
         <is>
@@ -8736,12 +8744,12 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
@@ -9555,7 +9563,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -9565,12 +9573,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -9605,7 +9613,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>0.09090909090909091</t>
+          <t>0.07142857142857142</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -9620,12 +9628,12 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>0.4444444444444444</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>0.38888888888888884</t>
+          <t>0.22222222222222224</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
@@ -10007,7 +10015,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -10017,12 +10025,12 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -10072,12 +10080,12 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
@@ -10087,12 +10095,12 @@
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -10149,7 +10157,7 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>promoted_from_screening; passes_stage1_default_epoch_rule; informative_but_bounds_wide</t>
+          <t>promoted_from_screening; passes_stage1_default_epoch_rule</t>
         </is>
       </c>
     </row>
@@ -10459,7 +10467,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -10469,12 +10477,12 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -10509,7 +10517,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>0.07142857142857142</t>
+          <t>0.0425531914893617</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -10524,12 +10532,12 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1346153846153846</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>0.46153846153846156</t>
+          <t>0.09615384615384615</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
@@ -10539,12 +10547,12 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -10605,7 +10613,7 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>passes_stage1_default_epoch_rule; informative_but_bounds_wide; prn_free_epoch</t>
+          <t>passes_stage1_default_epoch_rule; prn_free_epoch</t>
         </is>
       </c>
     </row>
@@ -11843,37 +11851,37 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>881</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>509</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>372</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>326</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>164</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -11893,7 +11901,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>0.5870535714285714</t>
+          <t>0.5777525539160046</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -11903,17 +11911,17 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>0.5723612622415669</t>
+          <t>0.5538628944504896</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>0.5973884657236126</t>
+          <t>0.5952121871599565</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>0.02502720348204568</t>
+          <t>0.041349292709466856</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -11938,12 +11946,12 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -12036,7 +12044,7 @@
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="25" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="21" customWidth="1" min="26" max="26"/>
     <col width="31" customWidth="1" min="27" max="27"/>
     <col width="36" customWidth="1" min="28" max="28"/>
     <col width="30" customWidth="1" min="29" max="29"/>
@@ -12164,7 +12172,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>manuscript/supplementary/Supplementary_Table_33_Sample_Frame_Reconciliation.tsv</t>
+          <t>manuscript/submission_data/audit_ledgers/supplementary_table_sources/Supplementary_Table_33_Sample_Frame_Reconciliation.tsv</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -14562,7 +14570,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>passes_stage1_default_epoch_rule; mixed_or_partial_prn_epoch; passes_stage1_default_epoch_rule; informative_but_bounds_wide; prn_free_epoch</t>
+          <t>passes_stage1_default_epoch_rule; mixed_or_partial_prn_epoch; passes_stage1_default_epoch_rule; prn_free_epoch</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -14582,7 +14590,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -14597,7 +14605,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>jpn_pre2012_mixed_ap</t>
+          <t>jpn_pre2012_mixed_ap; jpn_ap_without_prn</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -14612,7 +14620,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -14622,17 +14630,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.6219512195121951</t>
+          <t>0.8536585365853658</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.4615384615384615</t>
+          <t>0.2333333333333333</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -14773,12 +14781,12 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>jpn_pre2012_mixed_ap=23; jpn_ap_without_prn=28</t>
+          <t>jpn_pre2012_mixed_ap=23; jpn_ap_without_prn=47</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>jpn_pre2012_mixed_ap=0.233; jpn_ap_without_prn=0.462</t>
+          <t>jpn_pre2012_mixed_ap=0.233; jpn_ap_without_prn=0.096</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -15122,22 +15130,22 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>908</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>0.9705573080967402</t>
+          <t>0.9547844374342797</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -15182,7 +15190,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -15287,12 +15295,12 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>usa_wp_only=21; usa_transition_mixed=6; usa_ap_prn_background=896</t>
+          <t>usa_wp_only=21; usa_transition_mixed=6; usa_ap_prn_background=881</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>usa_wp_only=0.087; usa_transition_mixed=0.333; usa_ap_prn_background=0.025</t>
+          <t>usa_wp_only=0.087; usa_transition_mixed=0.333; usa_ap_prn_background=0.041</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -15329,7 +15337,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>promoted_from_screening; passes_stage1_default_epoch_rule; promoted_from_screening; passes_stage1_default_epoch_rule; informative_but_bounds_wide</t>
+          <t>promoted_from_screening; passes_stage1_default_epoch_rule</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -15349,7 +15357,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -15364,7 +15372,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>gbr_wp_only</t>
+          <t>gbr_wp_only; gbr_ap_prn_positive</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -15379,7 +15387,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -15389,17 +15397,17 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>0.5517241379310345</t>
+          <t>0.5862068965517241</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4285714285714285</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -15536,12 +15544,12 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>gbr_wp_only=8; gbr_ap_prn_positive=8</t>
+          <t>gbr_wp_only=8; gbr_ap_prn_positive=9</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>gbr_wp_only=0.429; gbr_ap_prn_positive=0.467</t>
+          <t>gbr_wp_only=0.429; gbr_ap_prn_positive=0.400</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
@@ -15881,7 +15889,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>711</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -15891,17 +15899,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>140</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>0.8343125734430082</t>
+          <t>0.8354876615746181</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>0.1617473435655254</t>
+          <t>0.1605667060212514</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -16042,12 +16050,12 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>chn_wp_only=0; chn_transition_mixed=0; chn_ap_mixed=710</t>
+          <t>chn_wp_only=0; chn_transition_mixed=0; chn_ap_mixed=711</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>chn_wp_only=1.000; chn_transition_mixed=NA; chn_ap_mixed=0.162</t>
+          <t>chn_wp_only=1.000; chn_transition_mixed=NA; chn_ap_mixed=0.161</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -16371,27 +16379,27 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>0.1111111111111111</t>
+          <t>0.8888888888888888</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -16528,12 +16536,12 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>esp_wp_only=0; esp_transition_mixed=0; esp_ap_with_prn=1; esp_booster_modified_uncertain=0</t>
+          <t>esp_wp_only=0; esp_transition_mixed=0; esp_ap_with_prn=1; esp_booster_modified_uncertain=7</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>esp_wp_only=NA; esp_transition_mixed=NA; esp_ap_with_prn=0.000; esp_booster_modified_uncertain=1.000</t>
+          <t>esp_wp_only=NA; esp_transition_mixed=NA; esp_ap_with_prn=0.000; esp_booster_modified_uncertain=0.125</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -16608,7 +16616,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -16618,17 +16626,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -16765,12 +16773,12 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>fin_wp_only=0; fin_ap_without_prn=0; fin_ap_with_prn=4</t>
+          <t>fin_wp_only=3; fin_ap_without_prn=0; fin_ap_with_prn=4</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fin_wp_only=1.000; fin_ap_without_prn=1.000; fin_ap_with_prn=0.000</t>
+          <t>fin_wp_only=0.769; fin_ap_without_prn=1.000; fin_ap_with_prn=0.000</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -16857,7 +16865,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -16867,17 +16875,17 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6363636363636364</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>0.3888888888888888</t>
+          <t>0.2222222222222222</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -17018,12 +17026,12 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>fra_wp_only=0; fra_ap_mixed=11</t>
+          <t>fra_wp_only=0; fra_ap_mixed=14</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fra_wp_only=1.000; fra_ap_mixed=0.389</t>
+          <t>fra_wp_only=1.000; fra_ap_mixed=0.222</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -18960,7 +18968,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>711</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -18970,12 +18978,12 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>698</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>136</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -19010,7 +19018,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>0.018309859154929577</t>
+          <t>0.01828410689170183</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -19025,12 +19033,12 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>0.1770956316410862</t>
+          <t>0.17591499409681227</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>0.1617473435655254</t>
+          <t>0.16056670602125148</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
@@ -20044,7 +20052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -20054,12 +20062,12 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -20092,7 +20100,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr">
         <is>
@@ -20101,12 +20113,12 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
@@ -20116,7 +20128,7 @@
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AG78" t="inlineStr">
@@ -20260,7 +20272,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -20270,12 +20282,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -20308,7 +20320,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr">
         <is>
@@ -20317,12 +20333,12 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
@@ -21136,7 +21152,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -21146,12 +21162,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -21186,7 +21202,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>0.09090909090909091</t>
+          <t>0.07142857142857142</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -21201,12 +21217,12 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>0.4444444444444444</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>0.38888888888888884</t>
+          <t>0.22222222222222224</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
@@ -21588,7 +21604,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -21598,12 +21614,12 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -21653,12 +21669,12 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
@@ -21668,12 +21684,12 @@
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -21730,7 +21746,7 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>promoted_from_screening; passes_stage1_default_epoch_rule; informative_but_bounds_wide</t>
+          <t>promoted_from_screening; passes_stage1_default_epoch_rule</t>
         </is>
       </c>
     </row>
@@ -22040,7 +22056,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -22050,12 +22066,12 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -22090,7 +22106,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>0.07142857142857142</t>
+          <t>0.0425531914893617</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -22105,12 +22121,12 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1346153846153846</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>0.46153846153846156</t>
+          <t>0.09615384615384615</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
@@ -22120,12 +22136,12 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -22186,7 +22202,7 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>passes_stage1_default_epoch_rule; informative_but_bounds_wide; prn_free_epoch</t>
+          <t>passes_stage1_default_epoch_rule; prn_free_epoch</t>
         </is>
       </c>
     </row>
@@ -23424,37 +23440,37 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>881</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>509</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>372</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>326</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>164</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -23474,7 +23490,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>0.5870535714285714</t>
+          <t>0.5777525539160046</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -23484,17 +23500,17 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>0.5723612622415669</t>
+          <t>0.5538628944504896</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>0.5973884657236126</t>
+          <t>0.5952121871599565</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>0.02502720348204568</t>
+          <t>0.041349292709466856</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -23519,12 +23535,12 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
@@ -23617,7 +23633,7 @@
     <col width="22" customWidth="1" min="23" max="23"/>
     <col width="25" customWidth="1" min="24" max="24"/>
     <col width="30" customWidth="1" min="25" max="25"/>
-    <col width="22" customWidth="1" min="26" max="26"/>
+    <col width="21" customWidth="1" min="26" max="26"/>
     <col width="31" customWidth="1" min="27" max="27"/>
     <col width="36" customWidth="1" min="28" max="28"/>
     <col width="30" customWidth="1" min="29" max="29"/>
@@ -23745,7 +23761,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>manuscript/supplementary/Supplementary_Table_33_Sample_Frame_Reconciliation.tsv</t>
+          <t>manuscript/submission_data/audit_ledgers/supplementary_table_sources/Supplementary_Table_33_Sample_Frame_Reconciliation.tsv</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -26143,7 +26159,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>passes_stage1_default_epoch_rule; mixed_or_partial_prn_epoch; passes_stage1_default_epoch_rule; informative_but_bounds_wide; prn_free_epoch</t>
+          <t>passes_stage1_default_epoch_rule; mixed_or_partial_prn_epoch; passes_stage1_default_epoch_rule; prn_free_epoch</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -26163,7 +26179,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -26178,7 +26194,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>jpn_pre2012_mixed_ap</t>
+          <t>jpn_pre2012_mixed_ap; jpn_ap_without_prn</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -26193,7 +26209,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>70</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -26203,17 +26219,17 @@
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.6219512195121951</t>
+          <t>0.8536585365853658</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.4615384615384615</t>
+          <t>0.2333333333333333</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -26354,12 +26370,12 @@
       </c>
       <c r="AU50" t="inlineStr">
         <is>
-          <t>jpn_pre2012_mixed_ap=23; jpn_ap_without_prn=28</t>
+          <t>jpn_pre2012_mixed_ap=23; jpn_ap_without_prn=47</t>
         </is>
       </c>
       <c r="AV50" t="inlineStr">
         <is>
-          <t>jpn_pre2012_mixed_ap=0.233; jpn_ap_without_prn=0.462</t>
+          <t>jpn_pre2012_mixed_ap=0.233; jpn_ap_without_prn=0.096</t>
         </is>
       </c>
       <c r="AW50" t="inlineStr">
@@ -26703,22 +26719,22 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>908</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>534</t>
+          <t>517</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>0.9705573080967402</t>
+          <t>0.9547844374342797</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -26763,7 +26779,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -26868,12 +26884,12 @@
       </c>
       <c r="AU52" t="inlineStr">
         <is>
-          <t>usa_wp_only=21; usa_transition_mixed=6; usa_ap_prn_background=896</t>
+          <t>usa_wp_only=21; usa_transition_mixed=6; usa_ap_prn_background=881</t>
         </is>
       </c>
       <c r="AV52" t="inlineStr">
         <is>
-          <t>usa_wp_only=0.087; usa_transition_mixed=0.333; usa_ap_prn_background=0.025</t>
+          <t>usa_wp_only=0.087; usa_transition_mixed=0.333; usa_ap_prn_background=0.041</t>
         </is>
       </c>
       <c r="AW52" t="inlineStr">
@@ -26910,7 +26926,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>promoted_from_screening; passes_stage1_default_epoch_rule; promoted_from_screening; passes_stage1_default_epoch_rule; informative_but_bounds_wide</t>
+          <t>promoted_from_screening; passes_stage1_default_epoch_rule</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -26930,7 +26946,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -26945,7 +26961,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>gbr_wp_only</t>
+          <t>gbr_wp_only; gbr_ap_prn_positive</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -26960,7 +26976,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -26970,17 +26986,17 @@
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>0.5517241379310345</t>
+          <t>0.5862068965517241</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4285714285714285</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
@@ -27117,12 +27133,12 @@
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>gbr_wp_only=8; gbr_ap_prn_positive=8</t>
+          <t>gbr_wp_only=8; gbr_ap_prn_positive=9</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
         <is>
-          <t>gbr_wp_only=0.429; gbr_ap_prn_positive=0.467</t>
+          <t>gbr_wp_only=0.429; gbr_ap_prn_positive=0.400</t>
         </is>
       </c>
       <c r="AW53" t="inlineStr">
@@ -27462,7 +27478,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>711</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -27472,17 +27488,17 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>140</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>0.8343125734430082</t>
+          <t>0.8354876615746181</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>0.1617473435655254</t>
+          <t>0.1605667060212514</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
@@ -27623,12 +27639,12 @@
       </c>
       <c r="AU55" t="inlineStr">
         <is>
-          <t>chn_wp_only=0; chn_transition_mixed=0; chn_ap_mixed=710</t>
+          <t>chn_wp_only=0; chn_transition_mixed=0; chn_ap_mixed=711</t>
         </is>
       </c>
       <c r="AV55" t="inlineStr">
         <is>
-          <t>chn_wp_only=1.000; chn_transition_mixed=NA; chn_ap_mixed=0.162</t>
+          <t>chn_wp_only=1.000; chn_transition_mixed=NA; chn_ap_mixed=0.161</t>
         </is>
       </c>
       <c r="AW55" t="inlineStr">
@@ -27952,27 +27968,27 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>0.1111111111111111</t>
+          <t>0.8888888888888888</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
@@ -28109,12 +28125,12 @@
       </c>
       <c r="AU57" t="inlineStr">
         <is>
-          <t>esp_wp_only=0; esp_transition_mixed=0; esp_ap_with_prn=1; esp_booster_modified_uncertain=0</t>
+          <t>esp_wp_only=0; esp_transition_mixed=0; esp_ap_with_prn=1; esp_booster_modified_uncertain=7</t>
         </is>
       </c>
       <c r="AV57" t="inlineStr">
         <is>
-          <t>esp_wp_only=NA; esp_transition_mixed=NA; esp_ap_with_prn=0.000; esp_booster_modified_uncertain=1.000</t>
+          <t>esp_wp_only=NA; esp_transition_mixed=NA; esp_ap_with_prn=0.000; esp_booster_modified_uncertain=0.125</t>
         </is>
       </c>
       <c r="AW57" t="inlineStr">
@@ -28189,7 +28205,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -28199,17 +28215,17 @@
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.35</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
@@ -28346,12 +28362,12 @@
       </c>
       <c r="AU58" t="inlineStr">
         <is>
-          <t>fin_wp_only=0; fin_ap_without_prn=0; fin_ap_with_prn=4</t>
+          <t>fin_wp_only=3; fin_ap_without_prn=0; fin_ap_with_prn=4</t>
         </is>
       </c>
       <c r="AV58" t="inlineStr">
         <is>
-          <t>fin_wp_only=1.000; fin_ap_without_prn=1.000; fin_ap_with_prn=0.000</t>
+          <t>fin_wp_only=0.769; fin_ap_without_prn=1.000; fin_ap_with_prn=0.000</t>
         </is>
       </c>
       <c r="AW58" t="inlineStr">
@@ -28438,7 +28454,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -28448,17 +28464,17 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>8</t>
         </is>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6363636363636364</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>0.3888888888888888</t>
+          <t>0.2222222222222222</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
@@ -28599,12 +28615,12 @@
       </c>
       <c r="AU59" t="inlineStr">
         <is>
-          <t>fra_wp_only=0; fra_ap_mixed=11</t>
+          <t>fra_wp_only=0; fra_ap_mixed=14</t>
         </is>
       </c>
       <c r="AV59" t="inlineStr">
         <is>
-          <t>fra_wp_only=1.000; fra_ap_mixed=0.389</t>
+          <t>fra_wp_only=1.000; fra_ap_mixed=0.222</t>
         </is>
       </c>
       <c r="AW59" t="inlineStr">
@@ -30541,7 +30557,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>710</t>
+          <t>711</t>
         </is>
       </c>
       <c r="Q73" t="inlineStr">
@@ -30551,12 +30567,12 @@
       </c>
       <c r="R73" t="inlineStr">
         <is>
-          <t>697</t>
+          <t>698</t>
         </is>
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>136</t>
         </is>
       </c>
       <c r="T73" t="inlineStr">
@@ -30591,7 +30607,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>0.018309859154929577</t>
+          <t>0.01828410689170183</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -30606,12 +30622,12 @@
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>0.1770956316410862</t>
+          <t>0.17591499409681227</t>
         </is>
       </c>
       <c r="AD73" t="inlineStr">
         <is>
-          <t>0.1617473435655254</t>
+          <t>0.16056670602125148</t>
         </is>
       </c>
       <c r="AE73" t="inlineStr">
@@ -31625,7 +31641,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="Q78" t="inlineStr">
@@ -31635,12 +31651,12 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="T78" t="inlineStr">
@@ -31673,7 +31689,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr"/>
       <c r="AB78" t="inlineStr">
         <is>
@@ -31682,12 +31702,12 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AD78" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.125</t>
         </is>
       </c>
       <c r="AE78" t="inlineStr">
@@ -31697,7 +31717,7 @@
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AG78" t="inlineStr">
@@ -31841,7 +31861,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="Q79" t="inlineStr">
@@ -31851,12 +31871,12 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>10</t>
         </is>
       </c>
       <c r="T79" t="inlineStr">
@@ -31889,7 +31909,11 @@
           <t>0.0</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr">
         <is>
@@ -31898,12 +31922,12 @@
       </c>
       <c r="AC79" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="AD79" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.7692307692307693</t>
         </is>
       </c>
       <c r="AE79" t="inlineStr">
@@ -32717,7 +32741,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q83" t="inlineStr">
@@ -32727,12 +32751,12 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4</t>
         </is>
       </c>
       <c r="T83" t="inlineStr">
@@ -32767,7 +32791,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>0.09090909090909091</t>
+          <t>0.07142857142857142</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -32782,12 +32806,12 @@
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>0.4444444444444444</t>
+          <t>0.2777777777777778</t>
         </is>
       </c>
       <c r="AD83" t="inlineStr">
         <is>
-          <t>0.38888888888888884</t>
+          <t>0.22222222222222224</t>
         </is>
       </c>
       <c r="AE83" t="inlineStr">
@@ -33169,7 +33193,7 @@
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="Q85" t="inlineStr">
@@ -33179,12 +33203,12 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="T85" t="inlineStr">
@@ -33234,12 +33258,12 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AD85" t="inlineStr">
         <is>
-          <t>0.4666666666666667</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="AE85" t="inlineStr">
@@ -33249,12 +33273,12 @@
       </c>
       <c r="AF85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AG85" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AH85" t="inlineStr">
@@ -33311,7 +33335,7 @@
       </c>
       <c r="AT85" t="inlineStr">
         <is>
-          <t>promoted_from_screening; passes_stage1_default_epoch_rule; informative_but_bounds_wide</t>
+          <t>promoted_from_screening; passes_stage1_default_epoch_rule</t>
         </is>
       </c>
     </row>
@@ -33621,7 +33645,7 @@
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>47</t>
         </is>
       </c>
       <c r="Q87" t="inlineStr">
@@ -33631,12 +33655,12 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>45</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>5</t>
         </is>
       </c>
       <c r="T87" t="inlineStr">
@@ -33671,7 +33695,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>0.07142857142857142</t>
+          <t>0.0425531914893617</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -33686,12 +33710,12 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.1346153846153846</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
         <is>
-          <t>0.46153846153846156</t>
+          <t>0.09615384615384615</t>
         </is>
       </c>
       <c r="AE87" t="inlineStr">
@@ -33701,12 +33725,12 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AH87" t="inlineStr">
@@ -33767,7 +33791,7 @@
       </c>
       <c r="AT87" t="inlineStr">
         <is>
-          <t>passes_stage1_default_epoch_rule; informative_but_bounds_wide; prn_free_epoch</t>
+          <t>passes_stage1_default_epoch_rule; prn_free_epoch</t>
         </is>
       </c>
     </row>
@@ -35005,37 +35029,37 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>896</t>
+          <t>881</t>
         </is>
       </c>
       <c r="Q93" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>509</t>
         </is>
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>372</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>38</t>
         </is>
       </c>
       <c r="T93" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>326</t>
         </is>
       </c>
       <c r="U93" t="inlineStr">
         <is>
-          <t>168</t>
+          <t>164</t>
         </is>
       </c>
       <c r="V93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="W93" t="inlineStr">
@@ -35055,7 +35079,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>0.5870535714285714</t>
+          <t>0.5777525539160046</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -35065,17 +35089,17 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>0.5723612622415669</t>
+          <t>0.5538628944504896</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>0.5973884657236126</t>
+          <t>0.5952121871599565</t>
         </is>
       </c>
       <c r="AD93" t="inlineStr">
         <is>
-          <t>0.02502720348204568</t>
+          <t>0.041349292709466856</t>
         </is>
       </c>
       <c r="AE93" t="inlineStr">
@@ -35100,12 +35124,12 @@
       </c>
       <c r="AI93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AK93" t="inlineStr">
